--- a/employee_information_forms/045_food_delivery_personnel_onboarding_form--employee_information_forms.xlsx
+++ b/employee_information_forms/045_food_delivery_personnel_onboarding_form--employee_information_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C79"/>
+  <dimension ref="A1:C73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
@@ -1743,12 +1743,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>urology</t>
+          <t>pathology</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Urology</t>
+          <t>Pathology</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>pathology</t>
+          <t>pulmonology</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Pathology</t>
+          <t>Pulmonology</t>
         </is>
       </c>
     </row>
@@ -1777,12 +1777,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>cardiology</t>
+          <t>dermatologist</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Cardiology</t>
+          <t>Dermatologist</t>
         </is>
       </c>
     </row>
@@ -1794,12 +1794,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>pulmonology</t>
+          <t>allergologist</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Pulmonology</t>
+          <t>Allergologist</t>
         </is>
       </c>
     </row>
@@ -1811,12 +1811,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>gastroenterology</t>
+          <t>hematologist</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Gastroenterology</t>
+          <t>Hematologist</t>
         </is>
       </c>
     </row>
@@ -1828,12 +1828,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>nephrology</t>
+          <t>gynecologist</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Nephrology</t>
+          <t>Gynecologist</t>
         </is>
       </c>
     </row>
@@ -1845,12 +1845,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>endocrinology</t>
+          <t>urologist</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Endocrinology</t>
+          <t>Urologist</t>
         </is>
       </c>
     </row>
@@ -1862,12 +1862,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>dermatologist</t>
+          <t>pathologist</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Dermatologist</t>
+          <t>Pathologist</t>
         </is>
       </c>
     </row>
@@ -1879,12 +1879,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>allergologist</t>
+          <t>orthopedic</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Allergologist</t>
+          <t>Orthopedic</t>
         </is>
       </c>
     </row>
@@ -1896,97 +1896,97 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>hematologist</t>
+          <t>othopedic</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Hematologist</t>
+          <t>Othopedic</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>medical_specialties_choices</t>
+          <t>medical_insurance_choices</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>gynecologist</t>
+          <t>blue_cross</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Gynecologist</t>
+          <t>Blue Cross</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>medical_specialties_choices</t>
+          <t>medical_insurance_choices</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>urologist</t>
+          <t>blue_shield</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Urologist</t>
+          <t>Blue Shield</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>medical_specialties_choices</t>
+          <t>medical_insurance_choices</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>pathologist</t>
+          <t>medicare</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Pathologist</t>
+          <t>Medicare</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>medical_specialties_choices</t>
+          <t>medical_insurance_choices</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>orthopedic</t>
+          <t>unitedhealthcare</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Orthopedic</t>
+          <t>UnitedHealthcare</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>medical_specialties_choices</t>
+          <t>medical_insurance_choices</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>othopedic</t>
+          <t>cigna</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Othopedic</t>
+          <t>Cigna</t>
         </is>
       </c>
     </row>
@@ -1998,12 +1998,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>blue_cross</t>
+          <t>aetna</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Blue Cross</t>
+          <t>Aetna</t>
         </is>
       </c>
     </row>
@@ -2015,114 +2015,114 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>blue_shield</t>
+          <t>humana</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Blue Shield</t>
+          <t>Humana</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>medical_insurance_choices</t>
+          <t>vehicle_make_choices</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>medicare</t>
+          <t>toyota</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Medicare</t>
+          <t>Toyota</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>medical_insurance_choices</t>
+          <t>vehicle_make_choices</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>unitedhealthcare</t>
+          <t>ford</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>UnitedHealthcare</t>
+          <t>Ford</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>medical_insurance_choices</t>
+          <t>vehicle_make_choices</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>cigna</t>
+          <t>honda</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Cigna</t>
+          <t>Honda</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>medical_insurance_choices</t>
+          <t>vehicle_make_choices</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>unitedhealthcare</t>
+          <t>nissan</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>UnitedHealthcare</t>
+          <t>Nissan</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>medical_insurance_choices</t>
+          <t>vehicle_make_choices</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>aetna</t>
+          <t>chevrolet</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Aetna</t>
+          <t>Chevrolet</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>medical_insurance_choices</t>
+          <t>vehicle_make_choices</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>humana</t>
+          <t>volkswagen</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Volkswagen</t>
         </is>
       </c>
     </row>
@@ -2134,12 +2134,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>toyota</t>
+          <t>kia</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Toyota</t>
+          <t>Kia</t>
         </is>
       </c>
     </row>
@@ -2151,12 +2151,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>ford</t>
+          <t>hyundai</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Ford</t>
+          <t>Hyundai</t>
         </is>
       </c>
     </row>
@@ -2168,12 +2168,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>honda</t>
+          <t>mercedes</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Honda</t>
+          <t>Mercedes</t>
         </is>
       </c>
     </row>
@@ -2185,114 +2185,114 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>nissan</t>
+          <t>bmw</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Nissan</t>
+          <t>BMW</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>vehicle_make_choices</t>
+          <t>vehicle_year_choices</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>chevrolet</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Chevrolet</t>
+          <t>2015</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>vehicle_make_choices</t>
+          <t>vehicle_year_choices</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>volkswagen</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Volkswagen</t>
+          <t>2016</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>vehicle_make_choices</t>
+          <t>vehicle_year_choices</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>kia</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Kia</t>
+          <t>2017</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>vehicle_make_choices</t>
+          <t>vehicle_year_choices</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>hyundai</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Hyundai</t>
+          <t>2018</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>vehicle_make_choices</t>
+          <t>vehicle_year_choices</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>mercedes</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Mercedes</t>
+          <t>2019</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>vehicle_make_choices</t>
+          <t>vehicle_year_choices</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>bmw</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>BMW</t>
+          <t>2020</t>
         </is>
       </c>
     </row>
@@ -2304,12 +2304,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2021</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2022</t>
         </is>
       </c>
     </row>
@@ -2338,112 +2338,10 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>vehicle_year_choices</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>vehicle_year_choices</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>vehicle_year_choices</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>vehicle_year_choices</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>vehicle_year_choices</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>vehicle_year_choices</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
